--- a/backtest_runs/20260410_193731/by_symbol/AKBL/AKBL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AKBL/AKBL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -633,7 +633,7 @@
         <v>-2855.599999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>100907.5</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>100907.5</v>
@@ -817,7 +817,7 @@
         <v>-1899.700000000009</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>110006.7</v>
@@ -863,7 +863,7 @@
         <v>-568.6999999999987</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>109438</v>
@@ -909,7 +909,7 @@
         <v>-1270.499999999997</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>108167.5</v>
@@ -955,7 +955,7 @@
         <v>-36.30000000000138</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>108131.2</v>
@@ -1047,7 +1047,7 @@
         <v>-1379.400000000001</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>112305.7</v>
@@ -1093,7 +1093,7 @@
         <v>-907.5</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>111398.2</v>
@@ -1185,7 +1185,7 @@
         <v>-3750.999999999993</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>110357.6</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>110357.6</v>
@@ -1277,7 +1277,7 @@
         <v>-4755.299999999991</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>105602.3</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>112184.7</v>
@@ -1461,7 +1461,7 @@
         <v>-290.400000000011</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>111894.3</v>
@@ -1553,7 +1553,7 @@
         <v>-580.8000000000048</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>111797.5</v>
